--- a/erp-server/erp-server-file/src/main/resources/excel/wms/fbaShipment.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/fbaShipment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FBA货件" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>货件单号</t>
   </si>
@@ -47,6 +47,9 @@
     <t>发货单号</t>
   </si>
   <si>
+    <t>装箱清单状态</t>
+  </si>
+  <si>
     <t>平台货件状态</t>
   </si>
   <si>
@@ -102,6 +105,9 @@
   </si>
   <si>
     <t>{.deliveryCode}</t>
+  </si>
+  <si>
+    <t>{.packingDownload}</t>
   </si>
   <si>
     <t>{.platformShipmentStatus}</t>
@@ -1349,24 +1355,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
     <col min="4" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="24.25" customWidth="1"/>
-    <col min="8" max="9" width="30" customWidth="1"/>
-    <col min="10" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="45.75" style="1" customWidth="1"/>
-    <col min="16" max="17" width="15" customWidth="1"/>
-    <col min="18" max="19" width="30" customWidth="1"/>
+    <col min="7" max="8" width="24.25" customWidth="1"/>
+    <col min="9" max="10" width="30" customWidth="1"/>
+    <col min="11" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="45.75" style="1" customWidth="1"/>
+    <col min="17" max="18" width="15" customWidth="1"/>
+    <col min="19" max="20" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:19">
+    <row r="1" ht="15" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1424,67 +1430,73 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:20">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:20">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1499,13 +1511,14 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:20">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1520,13 +1533,14 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="5"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:20">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1541,13 +1555,14 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="5"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:20">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1562,13 +1577,14 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="5"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:20">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1583,13 +1599,14 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="5"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:20">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1604,14 +1621,15 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="5"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
     </row>
-    <row r="18" spans="13:13">
-      <c r="M18" s="1"/>
+    <row r="18" spans="14:14">
+      <c r="N18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/fbaShipment.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/fbaShipment.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>货件单号</t>
   </si>
@@ -47,9 +47,6 @@
     <t>发货单号</t>
   </si>
   <si>
-    <t>装箱清单状态</t>
-  </si>
-  <si>
     <t>平台货件状态</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
   </si>
   <si>
     <t>{.deliveryCode}</t>
-  </si>
-  <si>
-    <t>{.packingDownload}</t>
   </si>
   <si>
     <t>{.platformShipmentStatus}</t>
@@ -1355,24 +1349,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:S18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="15" customWidth="1"/>
     <col min="4" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="24.25" customWidth="1"/>
-    <col min="9" max="10" width="30" customWidth="1"/>
-    <col min="11" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="30" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="45.75" style="1" customWidth="1"/>
-    <col min="17" max="18" width="15" customWidth="1"/>
-    <col min="19" max="20" width="30" customWidth="1"/>
+    <col min="7" max="7" width="24.25" customWidth="1"/>
+    <col min="8" max="9" width="30" customWidth="1"/>
+    <col min="10" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="45.75" style="1" customWidth="1"/>
+    <col min="16" max="17" width="15" customWidth="1"/>
+    <col min="18" max="19" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:20">
+    <row r="1" ht="15" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1430,73 +1424,67 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:19">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1511,14 +1499,13 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:19">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1533,14 +1520,13 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:19">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1555,14 +1541,13 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:19">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1577,14 +1562,13 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:19">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1599,14 +1583,13 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:19">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -1621,15 +1604,14 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
     </row>
-    <row r="18" spans="14:14">
-      <c r="N18" s="1"/>
+    <row r="18" spans="13:13">
+      <c r="M18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
